--- a/Proyecto/data/PowerFlow_Results_Study1/res_bus/vm_pu.xlsx
+++ b/Proyecto/data/PowerFlow_Results_Study1/res_bus/vm_pu.xlsx
@@ -427,34 +427,34 @@
         <v>1</v>
       </c>
       <c r="C2">
-        <v>0.9618578521552649</v>
+        <v>0.9618578521552648</v>
       </c>
       <c r="D2">
-        <v>0.931084123637413</v>
+        <v>0.9310841236374128</v>
       </c>
       <c r="E2">
-        <v>0.9431227051865163</v>
+        <v>0.943122705186516</v>
       </c>
       <c r="F2">
         <v>1</v>
       </c>
       <c r="G2">
-        <v>0.9066647553938588</v>
+        <v>0.9066647553938583</v>
       </c>
       <c r="H2">
-        <v>0.9318975969960448</v>
+        <v>0.9318975969960442</v>
       </c>
       <c r="N2">
-        <v>0.9507168689362474</v>
+        <v>0.9507168689362473</v>
       </c>
       <c r="O2">
-        <v>0.9087159117932031</v>
+        <v>0.9087159117932024</v>
       </c>
       <c r="P2">
-        <v>0.9317118969941677</v>
+        <v>0.9317118969941672</v>
       </c>
       <c r="Q2">
-        <v>0.8946871142105911</v>
+        <v>0.8946871142105904</v>
       </c>
     </row>
     <row r="3" spans="1:17">
@@ -465,34 +465,34 @@
         <v>1</v>
       </c>
       <c r="C3">
-        <v>0.9623149657779579</v>
+        <v>0.9623149657779582</v>
       </c>
       <c r="D3">
-        <v>0.9320893796183705</v>
+        <v>0.9320893796183706</v>
       </c>
       <c r="E3">
-        <v>0.9438652762240179</v>
+        <v>0.9438652762240182</v>
       </c>
       <c r="F3">
         <v>1</v>
       </c>
       <c r="G3">
-        <v>0.9083908122401168</v>
+        <v>0.9083908122401172</v>
       </c>
       <c r="H3">
         <v>0.9329037312531299</v>
       </c>
       <c r="N3">
-        <v>0.9514478690260506</v>
+        <v>0.9514478690260511</v>
       </c>
       <c r="O3">
-        <v>0.9103352305319491</v>
+        <v>0.9103352305319493</v>
       </c>
       <c r="P3">
-        <v>0.9327402804237824</v>
+        <v>0.9327402804237828</v>
       </c>
       <c r="Q3">
-        <v>0.8967316698219443</v>
+        <v>0.8967316698219447</v>
       </c>
     </row>
     <row r="4" spans="1:17">
@@ -503,34 +503,34 @@
         <v>1</v>
       </c>
       <c r="C4">
-        <v>0.9625864231448583</v>
+        <v>0.9625864231448582</v>
       </c>
       <c r="D4">
-        <v>0.9326988915720381</v>
+        <v>0.9326988915720374</v>
       </c>
       <c r="E4">
-        <v>0.9443152660751333</v>
+        <v>0.9443152660751332</v>
       </c>
       <c r="F4">
-        <v>0.9999999999999999</v>
+        <v>1</v>
       </c>
       <c r="G4">
-        <v>0.9094487358968941</v>
+        <v>0.9094487358968935</v>
       </c>
       <c r="H4">
-        <v>0.9335137757276767</v>
+        <v>0.933513775727676</v>
       </c>
       <c r="N4">
-        <v>0.9518908750929332</v>
+        <v>0.9518908750929331</v>
       </c>
       <c r="O4">
-        <v>0.9113273703933042</v>
+        <v>0.9113273703933038</v>
       </c>
       <c r="P4">
-        <v>0.9333691257905616</v>
+        <v>0.9333691257905612</v>
       </c>
       <c r="Q4">
-        <v>0.8979881885461163</v>
+        <v>0.8979881885461158</v>
       </c>
     </row>
     <row r="5" spans="1:17">
@@ -541,34 +541,34 @@
         <v>1</v>
       </c>
       <c r="C5">
-        <v>0.9627637591076534</v>
+        <v>0.9627637591076537</v>
       </c>
       <c r="D5">
-        <v>0.9331127389446402</v>
+        <v>0.9331127389446403</v>
       </c>
       <c r="E5">
-        <v>0.9446163344792136</v>
+        <v>0.9446163344792138</v>
       </c>
       <c r="F5">
-        <v>0.9999999999999997</v>
+        <v>1</v>
       </c>
       <c r="G5">
-        <v>0.9101912709464813</v>
+        <v>0.9101912709464817</v>
       </c>
       <c r="H5">
-        <v>0.933927984672132</v>
+        <v>0.9339279846721322</v>
       </c>
       <c r="N5">
-        <v>0.9521947040236665</v>
+        <v>0.9521947040236668</v>
       </c>
       <c r="O5">
-        <v>0.9120220250926439</v>
+        <v>0.912022025092644</v>
       </c>
       <c r="P5">
         <v>0.9338018828999183</v>
       </c>
       <c r="Q5">
-        <v>0.8988765501437311</v>
+        <v>0.8988765501437312</v>
       </c>
     </row>
     <row r="6" spans="1:17">
@@ -579,34 +579,34 @@
         <v>1</v>
       </c>
       <c r="C6">
-        <v>0.96243171167347</v>
+        <v>0.9624317116734702</v>
       </c>
       <c r="D6">
-        <v>0.932365778359497</v>
+        <v>0.9323657783594972</v>
       </c>
       <c r="E6">
-        <v>0.9440614604915469</v>
+        <v>0.944061460491547</v>
       </c>
       <c r="F6">
         <v>1</v>
       </c>
       <c r="G6">
-        <v>0.9089021016892447</v>
+        <v>0.9089021016892449</v>
       </c>
       <c r="H6">
-        <v>0.9331803714794313</v>
+        <v>0.9331803714794318</v>
       </c>
       <c r="N6">
-        <v>0.9516546953801756</v>
+        <v>0.9516546953801757</v>
       </c>
       <c r="O6">
-        <v>0.9108120720888681</v>
+        <v>0.9108120720888682</v>
       </c>
       <c r="P6">
-        <v>0.9330301856610203</v>
+        <v>0.9330301856610204</v>
       </c>
       <c r="Q6">
-        <v>0.8973469984492229</v>
+        <v>0.8973469984492235</v>
       </c>
     </row>
     <row r="7" spans="1:17">
@@ -617,34 +617,34 @@
         <v>1</v>
       </c>
       <c r="C7">
-        <v>0.9620444326364719</v>
+        <v>0.9620444326364721</v>
       </c>
       <c r="D7">
         <v>0.9315103408307918</v>
       </c>
       <c r="E7">
-        <v>0.9434266346600869</v>
+        <v>0.9434266346600868</v>
       </c>
       <c r="F7">
         <v>1</v>
       </c>
       <c r="G7">
-        <v>0.9074373701915197</v>
+        <v>0.9074373701915198</v>
       </c>
       <c r="H7">
-        <v>0.9323241865685916</v>
+        <v>0.9323241865685917</v>
       </c>
       <c r="N7">
-        <v>0.9510352517761791</v>
+        <v>0.9510352517761793</v>
       </c>
       <c r="O7">
-        <v>0.9094371765478766</v>
+        <v>0.9094371765478764</v>
       </c>
       <c r="P7">
-        <v>0.9321531036188591</v>
+        <v>0.9321531036188592</v>
       </c>
       <c r="Q7">
-        <v>0.8956127538947469</v>
+        <v>0.8956127538947467</v>
       </c>
     </row>
     <row r="8" spans="1:17">
@@ -655,34 +655,34 @@
         <v>1</v>
       </c>
       <c r="C8">
-        <v>0.961788990786999</v>
+        <v>0.9617889907869992</v>
       </c>
       <c r="D8">
-        <v>0.9309636409580354</v>
+        <v>0.9309636409580357</v>
       </c>
       <c r="E8">
-        <v>0.9430153170256297</v>
+        <v>0.9430153170256299</v>
       </c>
       <c r="F8">
-        <v>0.9999999999999999</v>
+        <v>1</v>
       </c>
       <c r="G8">
-        <v>0.9065302307248343</v>
+        <v>0.9065302307248346</v>
       </c>
       <c r="H8">
-        <v>0.9317770090528705</v>
+        <v>0.9317770090528704</v>
       </c>
       <c r="N8">
-        <v>0.9506434852448103</v>
+        <v>0.9506434852448107</v>
       </c>
       <c r="O8">
-        <v>0.9085836439636806</v>
+        <v>0.908583643963681</v>
       </c>
       <c r="P8">
-        <v>0.9315992668120598</v>
+        <v>0.9315992668120597</v>
       </c>
       <c r="Q8">
-        <v>0.8945465190474898</v>
+        <v>0.8945465190474899</v>
       </c>
     </row>
     <row r="9" spans="1:17">
@@ -693,34 +693,34 @@
         <v>1</v>
       </c>
       <c r="C9">
-        <v>0.9609455382690859</v>
+        <v>0.9609455382690858</v>
       </c>
       <c r="D9">
-        <v>0.9291669904326121</v>
+        <v>0.929166990432612</v>
       </c>
       <c r="E9">
-        <v>0.9416813977639268</v>
+        <v>0.9416813977639266</v>
       </c>
       <c r="F9">
         <v>1</v>
       </c>
       <c r="G9">
-        <v>0.903512464766242</v>
+        <v>0.9035124647662419</v>
       </c>
       <c r="H9">
-        <v>0.9299787888225189</v>
+        <v>0.9299787888225188</v>
       </c>
       <c r="N9">
-        <v>0.9493416269962907</v>
+        <v>0.9493416269962904</v>
       </c>
       <c r="O9">
-        <v>0.9057496003398252</v>
+        <v>0.9057496003398248</v>
       </c>
       <c r="P9">
-        <v>0.9297860335916904</v>
+        <v>0.9297860335916903</v>
       </c>
       <c r="Q9">
-        <v>0.8909912580762981</v>
+        <v>0.8909912580762978</v>
       </c>
     </row>
     <row r="10" spans="1:17">
@@ -731,7 +731,7 @@
         <v>1</v>
       </c>
       <c r="C10">
-        <v>0.9601212675085474</v>
+        <v>0.9601212675085472</v>
       </c>
       <c r="D10">
         <v>0.9274439775187788</v>
@@ -740,22 +740,22 @@
         <v>0.94041639198694</v>
       </c>
       <c r="F10">
-        <v>0.9999999999999997</v>
+        <v>1</v>
       </c>
       <c r="G10">
         <v>0.9006123063662107</v>
       </c>
       <c r="H10">
-        <v>0.9282542705397651</v>
+        <v>0.9282542705397652</v>
       </c>
       <c r="N10">
         <v>0.9480809549862154</v>
       </c>
       <c r="O10">
-        <v>0.903029760387942</v>
+        <v>0.9030297603879419</v>
       </c>
       <c r="P10">
-        <v>0.9280643071909306</v>
+        <v>0.9280643071909308</v>
       </c>
       <c r="Q10">
         <v>0.8875751614405805</v>
@@ -769,34 +769,34 @@
         <v>1</v>
       </c>
       <c r="C11">
-        <v>0.9597731299851013</v>
+        <v>0.959773129985102</v>
       </c>
       <c r="D11">
-        <v>0.926728292018772</v>
+        <v>0.9267282920187728</v>
       </c>
       <c r="E11">
-        <v>0.9398920993979527</v>
+        <v>0.9398920993979533</v>
       </c>
       <c r="F11">
-        <v>0.9999999999999998</v>
+        <v>1</v>
       </c>
       <c r="G11">
-        <v>0.8994158159941871</v>
+        <v>0.8994158159941879</v>
       </c>
       <c r="H11">
-        <v>0.9275379597567444</v>
+        <v>0.927537959756745</v>
       </c>
       <c r="N11">
-        <v>0.9475562295783851</v>
+        <v>0.9475562295783857</v>
       </c>
       <c r="O11">
-        <v>0.9019078573863052</v>
+        <v>0.901907857386306</v>
       </c>
       <c r="P11">
-        <v>0.9273550118995817</v>
+        <v>0.9273550118995821</v>
       </c>
       <c r="Q11">
-        <v>0.886168556943325</v>
+        <v>0.8861685569433255</v>
       </c>
     </row>
     <row r="12" spans="1:17">
@@ -807,34 +807,34 @@
         <v>1</v>
       </c>
       <c r="C12">
-        <v>0.9596659596784287</v>
+        <v>0.9596659596784285</v>
       </c>
       <c r="D12">
-        <v>0.9265059499044012</v>
+        <v>0.9265059499044008</v>
       </c>
       <c r="E12">
-        <v>0.9397336491512601</v>
+        <v>0.9397336491512597</v>
       </c>
       <c r="F12">
         <v>1</v>
       </c>
       <c r="G12">
-        <v>0.8990311592669253</v>
+        <v>0.899031159266925</v>
       </c>
       <c r="H12">
-        <v>0.9273154233856117</v>
+        <v>0.9273154233856112</v>
       </c>
       <c r="N12">
-        <v>0.9473894682343295</v>
+        <v>0.9473894682343292</v>
       </c>
       <c r="O12">
-        <v>0.9015484655763272</v>
+        <v>0.9015484655763268</v>
       </c>
       <c r="P12">
-        <v>0.9271342420968676</v>
+        <v>0.9271342420968673</v>
       </c>
       <c r="Q12">
-        <v>0.885713019088153</v>
+        <v>0.8857130190881527</v>
       </c>
     </row>
     <row r="13" spans="1:17">
@@ -848,22 +848,22 @@
         <v>0.9591653975009485</v>
       </c>
       <c r="D13">
-        <v>0.9254825409191079</v>
+        <v>0.925482540919108</v>
       </c>
       <c r="E13">
-        <v>0.9389989157471114</v>
+        <v>0.9389989157471115</v>
       </c>
       <c r="F13">
         <v>1</v>
       </c>
       <c r="G13">
-        <v>0.8972880024697806</v>
+        <v>0.897288002469781</v>
       </c>
       <c r="H13">
         <v>0.9262911202641997</v>
       </c>
       <c r="N13">
-        <v>0.9466262107116395</v>
+        <v>0.9466262107116398</v>
       </c>
       <c r="O13">
         <v>0.899918138858269</v>
@@ -872,7 +872,7 @@
         <v>0.9261244797644012</v>
       </c>
       <c r="Q13">
-        <v>0.8836560699256761</v>
+        <v>0.8836560699256765</v>
       </c>
     </row>
     <row r="14" spans="1:17">
@@ -883,34 +883,34 @@
         <v>1</v>
       </c>
       <c r="C14">
-        <v>0.9593714245763625</v>
+        <v>0.9593714245763627</v>
       </c>
       <c r="D14">
-        <v>0.9258977897351558</v>
+        <v>0.9258977897351564</v>
       </c>
       <c r="E14">
-        <v>0.9393029083464556</v>
+        <v>0.9393029083464561</v>
       </c>
       <c r="F14">
-        <v>1</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="G14">
-        <v>0.8979750226943162</v>
+        <v>0.8979750226943167</v>
       </c>
       <c r="H14">
-        <v>0.9267067318765194</v>
+        <v>0.9267067318765204</v>
       </c>
       <c r="N14">
-        <v>0.946930924894734</v>
+        <v>0.9469309248947344</v>
       </c>
       <c r="O14">
-        <v>0.9005623615203746</v>
+        <v>0.9005623615203751</v>
       </c>
       <c r="P14">
-        <v>0.9265320001077437</v>
+        <v>0.9265320001077442</v>
       </c>
       <c r="Q14">
-        <v>0.8844614475586787</v>
+        <v>0.8844614475586795</v>
       </c>
     </row>
     <row r="15" spans="1:17">
@@ -921,25 +921,25 @@
         <v>1</v>
       </c>
       <c r="C15">
-        <v>0.9605223911480758</v>
+        <v>0.9605223911480759</v>
       </c>
       <c r="D15">
-        <v>0.9282687194087442</v>
+        <v>0.9282687194087446</v>
       </c>
       <c r="E15">
         <v>0.9410293992131152</v>
       </c>
       <c r="F15">
-        <v>0.9999999999999999</v>
+        <v>1</v>
       </c>
       <c r="G15">
-        <v>0.9019692960521151</v>
+        <v>0.9019692960521154</v>
       </c>
       <c r="H15">
-        <v>0.929079732993575</v>
+        <v>0.9290797329935745</v>
       </c>
       <c r="N15">
-        <v>0.9486783284430738</v>
+        <v>0.9486783284430736</v>
       </c>
       <c r="O15">
         <v>0.904304745449575</v>
@@ -948,7 +948,7 @@
         <v>0.9288830279927839</v>
       </c>
       <c r="Q15">
-        <v>0.8891651094382259</v>
+        <v>0.8891651094382262</v>
       </c>
     </row>
     <row r="16" spans="1:17">
@@ -965,25 +965,25 @@
         <v>0.9293104204405922</v>
       </c>
       <c r="E16">
-        <v>0.9418023939366948</v>
+        <v>0.9418023939366953</v>
       </c>
       <c r="F16">
         <v>1</v>
       </c>
       <c r="G16">
-        <v>0.9036994177879208</v>
+        <v>0.9036994177879212</v>
       </c>
       <c r="H16">
-        <v>0.9301223441430109</v>
+        <v>0.9301223441430111</v>
       </c>
       <c r="N16">
-        <v>0.9494339267628162</v>
+        <v>0.949433926762816</v>
       </c>
       <c r="O16">
-        <v>0.9059298106640025</v>
+        <v>0.9059298106640028</v>
       </c>
       <c r="P16">
-        <v>0.9299237695134019</v>
+        <v>0.9299237695134021</v>
       </c>
       <c r="Q16">
         <v>0.8911972249173414</v>
@@ -997,31 +997,31 @@
         <v>1</v>
       </c>
       <c r="C17">
-        <v>0.9603548382694755</v>
+        <v>0.9603548382694753</v>
       </c>
       <c r="D17">
-        <v>0.9279072925568923</v>
+        <v>0.9279072925568921</v>
       </c>
       <c r="E17">
-        <v>0.9407772779683525</v>
+        <v>0.9407772779683521</v>
       </c>
       <c r="F17">
         <v>0.9999999999999999</v>
       </c>
       <c r="G17">
-        <v>0.9013177520825755</v>
+        <v>0.9013177520825754</v>
       </c>
       <c r="H17">
-        <v>0.9287179903688428</v>
+        <v>0.9287179903688423</v>
       </c>
       <c r="N17">
-        <v>0.9484028823913674</v>
+        <v>0.9484028823913671</v>
       </c>
       <c r="O17">
-        <v>0.9036976632767908</v>
+        <v>0.9036976632767904</v>
       </c>
       <c r="P17">
-        <v>0.9285183658790658</v>
+        <v>0.9285183658790654</v>
       </c>
       <c r="Q17">
         <v>0.8883864135141707</v>
@@ -1035,34 +1035,34 @@
         <v>1</v>
       </c>
       <c r="C18">
-        <v>0.9588718555298172</v>
+        <v>0.9588718555298174</v>
       </c>
       <c r="D18">
         <v>0.9248883955687488</v>
       </c>
       <c r="E18">
-        <v>0.9385748748527939</v>
+        <v>0.938574874852794</v>
       </c>
       <c r="F18">
-        <v>0.9999999999999999</v>
+        <v>1</v>
       </c>
       <c r="G18">
-        <v>0.8962753203723588</v>
+        <v>0.8962753203723587</v>
       </c>
       <c r="H18">
         <v>0.9256964558185182</v>
       </c>
       <c r="N18">
-        <v>0.9461807965081542</v>
+        <v>0.9461807965081543</v>
       </c>
       <c r="O18">
         <v>0.8989716152887025</v>
       </c>
       <c r="P18">
-        <v>0.9255413996388016</v>
+        <v>0.925541399638802</v>
       </c>
       <c r="Q18">
-        <v>0.8824612569504233</v>
+        <v>0.8824612569504234</v>
       </c>
     </row>
     <row r="19" spans="1:17">
@@ -1073,34 +1073,34 @@
         <v>1</v>
       </c>
       <c r="C19">
-        <v>0.9569572545993685</v>
+        <v>0.9569572545993692</v>
       </c>
       <c r="D19">
-        <v>0.9211280507665255</v>
+        <v>0.9211280507665267</v>
       </c>
       <c r="E19">
-        <v>0.9358479632476743</v>
+        <v>0.9358479632476751</v>
       </c>
       <c r="F19">
         <v>0.9999999999999999</v>
       </c>
       <c r="G19">
-        <v>0.890083648098308</v>
+        <v>0.8900836480983099</v>
       </c>
       <c r="H19">
-        <v>0.9219328256629755</v>
+        <v>0.9219328256629769</v>
       </c>
       <c r="N19">
-        <v>0.9434002121691407</v>
+        <v>0.9434002121691412</v>
       </c>
       <c r="O19">
-        <v>0.8931729439959356</v>
+        <v>0.8931729439959369</v>
       </c>
       <c r="P19">
-        <v>0.9219045856636899</v>
+        <v>0.9219045856636906</v>
       </c>
       <c r="Q19">
-        <v>0.8752168149077512</v>
+        <v>0.8752168149077534</v>
       </c>
     </row>
     <row r="20" spans="1:17">
@@ -1111,34 +1111,34 @@
         <v>1</v>
       </c>
       <c r="C20">
-        <v>0.9545878038711636</v>
+        <v>0.9545878038711637</v>
       </c>
       <c r="D20">
-        <v>0.9166242747418383</v>
+        <v>0.9166242747418387</v>
       </c>
       <c r="E20">
-        <v>0.9325988273350199</v>
+        <v>0.9325988273350203</v>
       </c>
       <c r="F20">
         <v>1</v>
       </c>
       <c r="G20">
-        <v>0.882775319095234</v>
+        <v>0.8827753190952345</v>
       </c>
       <c r="H20">
-        <v>0.91742511476096</v>
+        <v>0.9174251147609601</v>
       </c>
       <c r="N20">
-        <v>0.9400614499978662</v>
+        <v>0.9400614499978664</v>
       </c>
       <c r="O20">
-        <v>0.8863356946377356</v>
+        <v>0.8863356946377361</v>
       </c>
       <c r="P20">
-        <v>0.9176337758776776</v>
+        <v>0.9176337758776779</v>
       </c>
       <c r="Q20">
-        <v>0.8667039632062291</v>
+        <v>0.8667039632062294</v>
       </c>
     </row>
     <row r="21" spans="1:17">
@@ -1149,34 +1149,34 @@
         <v>1</v>
       </c>
       <c r="C21">
-        <v>0.9524181454469829</v>
+        <v>0.9524181454469833</v>
       </c>
       <c r="D21">
-        <v>0.9126063993274394</v>
+        <v>0.9126063993274399</v>
       </c>
       <c r="E21">
-        <v>0.9297226881005337</v>
+        <v>0.9297226881005342</v>
       </c>
       <c r="F21">
-        <v>0.9999999999999998</v>
+        <v>1</v>
       </c>
       <c r="G21">
-        <v>0.8763104198143807</v>
+        <v>0.8763104198143815</v>
       </c>
       <c r="H21">
-        <v>0.9134037289928503</v>
+        <v>0.9134037289928509</v>
       </c>
       <c r="N21">
-        <v>0.9370711121402977</v>
+        <v>0.9370711121402981</v>
       </c>
       <c r="O21">
-        <v>0.8802975836686415</v>
+        <v>0.8802975836686419</v>
       </c>
       <c r="P21">
-        <v>0.9138902901859963</v>
+        <v>0.9138902901859965</v>
       </c>
       <c r="Q21">
-        <v>0.8591959784647831</v>
+        <v>0.8591959784647841</v>
       </c>
     </row>
     <row r="22" spans="1:17">
@@ -1187,34 +1187,34 @@
         <v>1</v>
       </c>
       <c r="C22">
-        <v>0.9546298943183209</v>
+        <v>0.954629894318321</v>
       </c>
       <c r="D22">
         <v>0.9167019708115081</v>
       </c>
       <c r="E22">
-        <v>0.9326484181413177</v>
+        <v>0.9326484181413175</v>
       </c>
       <c r="F22">
-        <v>1</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="G22">
-        <v>0.8829153733171943</v>
+        <v>0.8829153733171941</v>
       </c>
       <c r="H22">
         <v>0.9175028787124468</v>
       </c>
       <c r="N22">
-        <v>0.9401250615699767</v>
+        <v>0.940125061569977</v>
       </c>
       <c r="O22">
         <v>0.8864651207639782</v>
       </c>
       <c r="P22">
-        <v>0.9177058395801145</v>
+        <v>0.9177058395801142</v>
       </c>
       <c r="Q22">
-        <v>0.8668707305727863</v>
+        <v>0.8668707305727861</v>
       </c>
     </row>
     <row r="23" spans="1:17">
@@ -1225,34 +1225,34 @@
         <v>1</v>
       </c>
       <c r="C23">
-        <v>0.9575491342003235</v>
+        <v>0.9575491342003236</v>
       </c>
       <c r="D23">
-        <v>0.9222791319124714</v>
+        <v>0.9222791319124711</v>
       </c>
       <c r="E23">
         <v>0.9366718890140954</v>
       </c>
       <c r="F23">
-        <v>0.9999999999999997</v>
+        <v>1</v>
       </c>
       <c r="G23">
-        <v>0.8919948088112305</v>
+        <v>0.8919948088112304</v>
       </c>
       <c r="H23">
-        <v>0.9230849124901723</v>
+        <v>0.9230849124901719</v>
       </c>
       <c r="N23">
-        <v>0.9442606679282235</v>
+        <v>0.9442606679282236</v>
       </c>
       <c r="O23">
-        <v>0.8949598037881261</v>
+        <v>0.8949598037881259</v>
       </c>
       <c r="P23">
-        <v>0.9230106698783925</v>
+        <v>0.9230106698783922</v>
       </c>
       <c r="Q23">
-        <v>0.8774562658563601</v>
+        <v>0.8774562658563599</v>
       </c>
     </row>
     <row r="24" spans="1:17">
@@ -1263,34 +1263,34 @@
         <v>1</v>
       </c>
       <c r="C24">
-        <v>0.9596004415628332</v>
+        <v>0.9596004415628336</v>
       </c>
       <c r="D24">
-        <v>0.9263650144924372</v>
+        <v>0.926365014492438</v>
       </c>
       <c r="E24">
-        <v>0.9396405119638821</v>
+        <v>0.9396405119638825</v>
       </c>
       <c r="F24">
         <v>1</v>
       </c>
       <c r="G24">
-        <v>0.89876449198204</v>
+        <v>0.898764491982041</v>
       </c>
       <c r="H24">
-        <v>0.9271743648406247</v>
+        <v>0.9271743648406257</v>
       </c>
       <c r="N24">
-        <v>0.9472775642296203</v>
+        <v>0.9472775642296205</v>
       </c>
       <c r="O24">
-        <v>0.9013013529303129</v>
+        <v>0.9013013529303139</v>
       </c>
       <c r="P24">
-        <v>0.9269927991617543</v>
+        <v>0.9269927991617547</v>
       </c>
       <c r="Q24">
-        <v>0.8853914293723989</v>
+        <v>0.8853914293723999</v>
       </c>
     </row>
     <row r="25" spans="1:17">
@@ -1301,34 +1301,34 @@
         <v>1</v>
       </c>
       <c r="C25">
-        <v>0.9634611731387283</v>
+        <v>0.9634611731387276</v>
       </c>
       <c r="D25">
-        <v>0.9335663218369108</v>
+        <v>0.9335663218369094</v>
       </c>
       <c r="E25">
-        <v>0.9457869767249842</v>
+        <v>0.9457869767249832</v>
       </c>
       <c r="F25">
-        <v>1</v>
+        <v>0.9999999999999999</v>
       </c>
       <c r="G25">
-        <v>0.9079593111021923</v>
+        <v>0.907959311102191</v>
       </c>
       <c r="H25">
-        <v>0.9343819638525467</v>
+        <v>0.9343819638525451</v>
       </c>
       <c r="N25">
-        <v>0.9518380184970721</v>
+        <v>0.9518380184970714</v>
       </c>
       <c r="O25">
-        <v>0.910181835728075</v>
+        <v>0.9101818357280737</v>
       </c>
       <c r="P25">
-        <v>0.9338973239034482</v>
+        <v>0.9338973239034475</v>
       </c>
       <c r="Q25">
-        <v>0.8954533792564916</v>
+        <v>0.8954533792564903</v>
       </c>
     </row>
   </sheetData>
